--- a/atividades/PID - Bases de Ciencia da Computacao 5 - 2.2026.xlsx
+++ b/atividades/PID - Bases de Ciencia da Computacao 5 - 2.2026.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B8" s="49" t="inlineStr">
         <is>
-          <t>Douglas de Oliveira Matos</t>
+          <t>Douglas de Oliveira Matos Braga</t>
         </is>
       </c>
       <c r="C8" s="50" t="n"/>
@@ -1727,7 +1727,7 @@
           <t>BÁSICA
 GRUS, Joel. Data science do zero: noções fundamentais com Python. 2. ed. Rio de Janeiro: Alta Books, 2021.
 GRUS, Joel. Data science from scratch: first principles with Python. 2nd ed. Sebastopol: O'Reilly Media, 2019.
-MATOS, Douglas de Oliveira. Bases de Ciência da Computação 5: ciência de dados. Brasília: UnDF, 2026. Material didático da unidade curricular. Disponível em: https://bragad.github.io/UnDF-Bases5-CienciaDeDados-202602/
+BRAGA, Douglas de Oliveira Matos. Bases de Ciência da Computação 5: ciência de dados. Brasília: UnDF, 2026. Material didático da unidade curricular. Disponível em: https://bragad.github.io/UnDF-Bases5-CienciaDeDados-202602/
 COMPLEMENTAR
 GÉRON, Aurélien. Mãos à obra: aprendizado de máquina com Scikit-Learn, Keras &amp; TensorFlow. 2. ed. Rio de Janeiro: Alta Books, 2021.
 VANDERPLAS, Jake. Python data science handbook: essential tools for working with data. 2nd ed. Sebastopol: O'Reilly Media, 2023.

--- a/atividades/PID - Bases de Ciencia da Computacao 5 - 2.2026.xlsx
+++ b/atividades/PID - Bases de Ciencia da Computacao 5 - 2.2026.xlsx
@@ -1239,16 +1239,17 @@
       <c r="G19" s="50" t="n"/>
       <c r="H19" s="51" t="n"/>
     </row>
-    <row r="20" ht="231" customHeight="1" s="46">
+    <row r="20" ht="426" customHeight="1" s="46">
       <c r="A20" s="57" t="n"/>
       <c r="B20" s="61" t="inlineStr">
         <is>
           <t>A avaliação da disciplina será processual, contínua e formativa, considerando a participação do estudante nas atividades presenciais e assíncronas, o desenvolvimento das competências previstas e a aplicação prática dos conceitos em situações-problema.
-São instrumentos avaliativos:
-Atividades práticas realizadas ao longo do semestre, com implementação e análise crítica de algoritmos, compondo a avaliação processual;
-Prova individual, aplicada em 16/12/2026, abrangendo os fundamentos e os algoritmos construídos ao longo da disciplina;
-Seminário em grupo, apresentado em 23/12/2026, com instruções disponibilizadas em 07/10/2026 e horário protegido para estudo em 14/10/2026, destinado à investigação e apresentação de tema correlato aos conteúdos da unidade curricular.
-A devolutiva da prova ocorrerá em 30/12/2026, em aula dedicada à revisão coletiva das questões, tratada como momento formativo e não apenas como divulgação de resultados.</t>
+São quatro os instrumentos avaliativos, totalizando 100%:
+1. Lista de exercícios I — peso 10% — entrega até 09/09/2026 (aula 4). Revisão dos pré-requisitos da unidade curricular: álgebra linear, cálculo e estatística. Além da nota, tem função diagnóstica: identificar cedo, ainda no início do semestre, os conteúdos que precisam ser retomados antes que a carga conceitual aumente.
+2. Lista de exercícios II — peso 10% — entrega até 09/12/2026 (aula 17). Abrange o conteúdo da unidade curricular e encerra antes da prova, funcionando como estudo dirigido para ela.
+3. Prova individual — peso 40% — aplicada em 16/12/2026 (aula 18), abrangendo os fundamentos e os algoritmos construídos ao longo da disciplina.
+4. Seminário em grupo — peso 40% — apresentado em 23/12/2026 (aula 19), a partir de um problema real extraído da plataforma Kaggle. Cada grupo seleciona uma competição, analisa o problema e os dados, aplica os métodos construídos na disciplina e apresenta o percurso, incluindo as tentativas que não funcionaram. O critério de avaliação não é o desempenho no ranking da plataforma, e sim a qualidade do raciocínio: a justificativa da escolha do método, o que os dados sustentam e os limites do resultado obtido. As instruções são disponibilizadas em 07/10/2026 (aula 8), com horário protegido para estudo (HPE) em 14/10/2026 (aula 9) destinado ao trabalho dos grupos.
+A devolutiva da prova ocorre em 30/12/2026, em aula dedicada à revisão coletiva das questões, tratada como momento formativo e não apenas como divulgação de resultados.</t>
         </is>
       </c>
       <c r="C20" s="59" t="n"/>
@@ -1333,14 +1334,14 @@
       <c r="G25" s="59" t="n"/>
       <c r="H25" s="60" t="n"/>
     </row>
-    <row r="26" ht="51" customHeight="1" s="46">
+    <row r="26" ht="66" customHeight="1" s="46">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="79" t="n">
         <v>46274</v>
       </c>
       <c r="C26" s="80" t="inlineStr">
         <is>
-          <t>Capítulo 4 — Álgebra Linear: vetores e matrizes construídos com listas de Python; soma, produto escalar, magnitude e distância. Representação de dados que sustenta todos os modelos seguintes.</t>
+          <t>Capítulo 4 — Álgebra Linear: vetores e matrizes construídos com listas de Python; soma, produto escalar, magnitude e distância. Representação de dados que sustenta todos os modelos seguintes. Entrega da Lista de exercícios I (revisão de pré-requisitos).</t>
         </is>
       </c>
       <c r="D26" s="59" t="n"/>
@@ -1548,7 +1549,7 @@
       </c>
       <c r="C39" s="80" t="inlineStr">
         <is>
-          <t>Capítulo 17 — Clustering: a ideia; o modelo k-means; escolha do número de grupos; agrupamento de cores em imagens; clustering hierárquico. Encerramento do conteúdo e revisão geral para a prova.</t>
+          <t>Capítulo 17 — Clustering: a ideia; o modelo k-means; escolha do número de grupos; agrupamento de cores em imagens; clustering hierárquico. Encerramento do conteúdo e revisão geral para a prova. Entrega da Lista de exercícios II.</t>
         </is>
       </c>
       <c r="D39" s="39" t="n"/>

--- a/atividades/PID - Bases de Ciencia da Computacao 5 - 2.2026.xlsx
+++ b/atividades/PID - Bases de Ciencia da Computacao 5 - 2.2026.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="B7" s="49" t="inlineStr">
         <is>
-          <t>Bases de Ciência da Computação 5 — 80 horas (20 encontros semanais de 4 horas-aula, às quartas-feiras)</t>
+          <t>Bases de Ciência da Computação 5 — 80 horas (20 encontros semanais de 4 horas-aula, às quartas-feiras; o conteúdo ocupa de 19/08 a 23/12/2026)</t>
         </is>
       </c>
       <c r="C7" s="50" t="n"/>
@@ -1239,17 +1239,17 @@
       <c r="G19" s="50" t="n"/>
       <c r="H19" s="51" t="n"/>
     </row>
-    <row r="20" ht="426" customHeight="1" s="46">
+    <row r="20" ht="441" customHeight="1" s="46">
       <c r="A20" s="57" t="n"/>
       <c r="B20" s="61" t="inlineStr">
         <is>
           <t>A avaliação da disciplina será processual, contínua e formativa, considerando a participação do estudante nas atividades presenciais e assíncronas, o desenvolvimento das competências previstas e a aplicação prática dos conceitos em situações-problema.
 São quatro os instrumentos avaliativos, totalizando 100%:
-1. Lista de exercícios I — peso 10% — entrega até 09/09/2026 (aula 4). Revisão dos pré-requisitos da unidade curricular: álgebra linear, cálculo e estatística. Além da nota, tem função diagnóstica: identificar cedo, ainda no início do semestre, os conteúdos que precisam ser retomados antes que a carga conceitual aumente.
-2. Lista de exercícios II — peso 10% — entrega até 09/12/2026 (aula 17). Abrange o conteúdo da unidade curricular e encerra antes da prova, funcionando como estudo dirigido para ela.
-3. Prova individual — peso 40% — aplicada em 16/12/2026 (aula 18), abrangendo os fundamentos e os algoritmos construídos ao longo da disciplina.
-4. Seminário em grupo — peso 40% — apresentado em 23/12/2026 (aula 19), a partir de um problema real extraído da plataforma Kaggle. Cada grupo seleciona uma competição, analisa o problema e os dados, aplica os métodos construídos na disciplina e apresenta o percurso, incluindo as tentativas que não funcionaram. O critério de avaliação não é o desempenho no ranking da plataforma, e sim a qualidade do raciocínio: a justificativa da escolha do método, o que os dados sustentam e os limites do resultado obtido. As instruções são disponibilizadas em 07/10/2026 (aula 8), com horário protegido para estudo (HPE) em 14/10/2026 (aula 9) destinado ao trabalho dos grupos.
-A devolutiva da prova ocorre em 30/12/2026, em aula dedicada à revisão coletiva das questões, tratada como momento formativo e não apenas como divulgação de resultados.</t>
+1. Lista de exercícios I — peso 10% — entrega até 16/09/2026 (aula 5). Revisão dos pré-requisitos da unidade curricular: álgebra linear, cálculo e estatística. Além da nota, tem função diagnóstica: identificar cedo, ainda no início do semestre, os conteúdos que precisam ser retomados antes que a carga conceitual aumente.
+2. Lista de exercícios II — peso 10% — entrega até 09/12/2026 (aula 17), no dia da prova. Abrange o conteúdo da unidade curricular e encerra antes da prova, funcionando como estudo dirigido para ela.
+3. Prova individual — peso 40% — aplicada em 09/12/2026 (aula 17), abrangendo os fundamentos e os algoritmos construídos ao longo da disciplina.
+4. Seminário em grupo — peso 40% — apresentado em 16/12/2026 (aula 18), a partir de um problema real extraído da plataforma Kaggle. Cada grupo seleciona uma competição, analisa o problema e os dados, aplica os métodos construídos na disciplina e apresenta o percurso, incluindo as tentativas que não funcionaram. O critério de avaliação não é o desempenho no ranking da plataforma, e sim a qualidade do raciocínio: a justificativa da escolha do método, o que os dados sustentam e os limites do resultado obtido. As instruções são disponibilizadas em 07/10/2026 (aula 8), com horário protegido para estudo (HPE) em 14/10/2026 (aula 9) destinado ao trabalho dos grupos.
+A devolutiva da prova ocorre em 23/12/2026, em aula dedicada à revisão coletiva das questões, tratada como momento formativo e não apenas como divulgação de resultados.</t>
         </is>
       </c>
       <c r="C20" s="59" t="n"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C24" s="80" t="inlineStr">
         <is>
-          <t>Capítulo 2 — Um Curso Rápido de Python: ambiente e sintaxe; funções, strings e exceções; estruturas de dados; controle de fluxo; testes, classes e geradores; ferramentas funcionais e anotações de tipo.</t>
+          <t>Capítulo 2 — Um Curso Rápido de Python: ambiente e sintaxe; funções, strings e exceções; estruturas de dados; controle de fluxo; testes, classes e geradores; ferramentas funcionais e anotações de tipo. Ambientação ao Google Colab.</t>
         </is>
       </c>
       <c r="D24" s="59" t="n"/>
@@ -1334,14 +1334,14 @@
       <c r="G25" s="59" t="n"/>
       <c r="H25" s="60" t="n"/>
     </row>
-    <row r="26" ht="66" customHeight="1" s="46">
+    <row r="26" ht="51" customHeight="1" s="46">
       <c r="A26" s="36" t="n"/>
       <c r="B26" s="79" t="n">
         <v>46274</v>
       </c>
       <c r="C26" s="80" t="inlineStr">
         <is>
-          <t>Capítulo 4 — Álgebra Linear: vetores e matrizes construídos com listas de Python; soma, produto escalar, magnitude e distância. Representação de dados que sustenta todos os modelos seguintes. Entrega da Lista de exercícios I (revisão de pré-requisitos).</t>
+          <t>Capítulo 4 — Álgebra Linear: vetores e matrizes construídos com listas de Python; soma, produto escalar, magnitude e distância. Representação de dados que sustenta todos os modelos seguintes.</t>
         </is>
       </c>
       <c r="D26" s="59" t="n"/>
@@ -1350,14 +1350,14 @@
       <c r="G26" s="59" t="n"/>
       <c r="H26" s="60" t="n"/>
     </row>
-    <row r="27" ht="51" customHeight="1" s="46">
+    <row r="27" ht="66" customHeight="1" s="46">
       <c r="A27" s="36" t="n"/>
       <c r="B27" s="79" t="n">
         <v>46281</v>
       </c>
       <c r="C27" s="80" t="inlineStr">
         <is>
-          <t>Capítulo 5 — Gradiente Descendente: a ideia por trás do gradiente; estimando e usando o gradiente; escolhendo o tamanho do passo; ajustando modelos; minibatch e gradiente estocástico.</t>
+          <t>Capítulo 5 — Gradiente Descendente: a ideia por trás do gradiente; estimando e usando o gradiente; escolhendo o tamanho do passo; ajustando modelos; minibatch e gradiente estocástico. Entrega da Lista de exercícios I (revisão de pré-requisitos).</t>
         </is>
       </c>
       <c r="D27" s="59" t="n"/>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C38" s="80" t="inlineStr">
         <is>
-          <t>Capítulo 16 — Deep Learning: o tensor; a abstração de camada; a camada linear; redes como sequência de camadas; perda e otimização; funções de ativação; softmax e dropout; exemplo com reconhecimento de dígitos manuscritos.</t>
+          <t>Capítulo 17 — Clustering: a ideia; o modelo k-means; escolha do número de grupos; agrupamento de cores em imagens; clustering hierárquico. Encerramento do conteúdo e revisão geral para a prova.</t>
         </is>
       </c>
       <c r="D38" s="39" t="n"/>
@@ -1542,14 +1542,14 @@
       <c r="G38" s="39" t="n"/>
       <c r="H38" s="39" t="n"/>
     </row>
-    <row r="39" ht="51" customHeight="1" s="46">
+    <row r="39" ht="36" customHeight="1" s="46">
       <c r="A39" s="36" t="n"/>
       <c r="B39" s="79" t="n">
         <v>46365</v>
       </c>
       <c r="C39" s="80" t="inlineStr">
         <is>
-          <t>Capítulo 17 — Clustering: a ideia; o modelo k-means; escolha do número de grupos; agrupamento de cores em imagens; clustering hierárquico. Encerramento do conteúdo e revisão geral para a prova. Entrega da Lista de exercícios II.</t>
+          <t>AVALIAÇÃO — Prova individual, abrangendo os fundamentos e os algoritmos construídos ao longo da unidade curricular. Entrega da Lista de exercícios II.</t>
         </is>
       </c>
       <c r="D39" s="39" t="n"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C40" s="80" t="inlineStr">
         <is>
-          <t>AVALIAÇÃO — Prova individual, abrangendo os fundamentos e os algoritmos construídos ao longo da unidade curricular.</t>
+          <t>AVALIAÇÃO — Apresentação dos seminários pelos grupos, com arguição e discussão coletiva.</t>
         </is>
       </c>
       <c r="D40" s="59" t="n"/>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C41" s="80" t="inlineStr">
         <is>
-          <t>AVALIAÇÃO — Apresentação dos seminários pelos grupos, com arguição e discussão coletiva.</t>
+          <t>Revisão da prova: devolutiva e correção coletiva das questões, com retomada dos pontos de maior dificuldade.</t>
         </is>
       </c>
       <c r="D41" s="59" t="n"/>
@@ -1590,14 +1590,14 @@
       <c r="G41" s="59" t="n"/>
       <c r="H41" s="60" t="n"/>
     </row>
-    <row r="42" ht="36" customHeight="1" s="46">
+    <row r="42" ht="28" customHeight="1" s="46">
       <c r="A42" s="36" t="n"/>
       <c r="B42" s="79" t="n">
         <v>46386</v>
       </c>
       <c r="C42" s="80" t="inlineStr">
         <is>
-          <t>Revisão da prova: devolutiva e correção coletiva das questões, com retomada dos pontos de maior dificuldade.</t>
+          <t>Sem aula.</t>
         </is>
       </c>
       <c r="D42" s="59" t="n"/>
